--- a/data/lseg_excel/SO-PREMP-C1.xlsx
+++ b/data/lseg_excel/SO-PREMP-C1.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1150</v>
+        <v>-1100</v>
       </c>
     </row>
     <row r="3">
